--- a/output/pdf_financials_xlsx/CIGI.xlsx
+++ b/output/pdf_financials_xlsx/CIGI.xlsx
@@ -939,25 +939,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-2.855</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-1.417</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-1.167</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-1.046</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-1.048</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.865</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1820,25 +1820,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>56.905</v>
+        <v>59.76</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>31.787</v>
+        <v>33.204</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>77.128</v>
+        <v>78.078</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>74.93600000000001</v>
+        <v>76.10299999999999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>62.126</v>
+        <v>63.172</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>35.262</v>
+        <v>36.31</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>72.114</v>
+        <v>72.979</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>72.467</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>88.651</v>
+        <v>91.506</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>78.17</v>
+        <v>79.587</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>147.308</v>
@@ -1935,10 +1935,10 @@
         <v>155.66</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>67.93300000000001</v>
+        <v>68.98099999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>108.147</v>
+        <v>109.012</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>111.091</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>6.702376992167418</v>
+        <v>6.918226630779932</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4.589536772070817</v>
+        <v>4.672732033757197</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>7.416309254880124</v>
@@ -1986,10 +1986,10 @@
         <v>7.41595826939376</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.199466069873207</v>
+        <v>5.279678049930427</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>6.834922715514599</v>
+        <v>6.889590973986125</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>6.451330034042088</v>
@@ -75902,7 +75902,7 @@
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E828" s="5" t="n">
@@ -75980,7 +75980,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E829" s="5" t="n">
@@ -84670,7 +84670,7 @@
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E933" s="5" t="n">

--- a/output/pdf_financials_xlsx/CIGI.xlsx
+++ b/output/pdf_financials_xlsx/CIGI.xlsx
@@ -1871,46 +1871,46 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>31.746</v>
+        <v>12.932</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>46.383</v>
+        <v>19.55</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>47.886</v>
+        <v>19.606</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>50.926</v>
+        <v>20.265</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>53.502</v>
+        <v>17.389</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>32.671</v>
+        <v>13.535</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>36.033</v>
+        <v>15.549</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>38.624</v>
+        <v>17.013</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>44.924</v>
+        <v>21.293</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>145.094</v>
+        <v>99.221</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>177.421</v>
+        <v>128.741</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>202.536</v>
+        <v>147.928</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>221.602</v>
+        <v>155.363</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>256.015</v>
+        <v>178.66</v>
       </c>
     </row>
     <row r="29">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>91.506</v>
+        <v>72.69199999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>79.587</v>
+        <v>52.754</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>147.308</v>
@@ -1935,16 +1935,16 @@
         <v>155.66</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>68.98099999999999</v>
+        <v>49.845</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>109.012</v>
+        <v>88.52800000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>111.091</v>
+        <v>89.48</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>184.324</v>
+        <v>160.693</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>466.975</v>
+        <v>418.295</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>415.313</v>
+        <v>360.705</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>532.715</v>
+        <v>466.476</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>560.722</v>
+        <v>483.367</v>
       </c>
     </row>
     <row r="30">
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>6.918226630779932</v>
+        <v>5.495811534157922</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4.672732033757197</v>
+        <v>3.097306164434231</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>7.416309254880124</v>
@@ -1986,16 +1986,16 @@
         <v>7.41595826939376</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.279678049930427</v>
+        <v>3.815044032397068</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>6.889590973986125</v>
+        <v>5.594996053141339</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>6.451330034042088</v>
+        <v>5.196325637955244</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.718019068667871</v>
+        <v>8.472134058513522</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -2003,16 +2003,16 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>10.47149593664025</v>
+        <v>9.379890556918319</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>9.580149757528071</v>
+        <v>8.320490613800105</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>11.04753937350789</v>
+        <v>9.673863091515098</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>10.08771850918473</v>
+        <v>8.696056571044293</v>
       </c>
     </row>
     <row r="31">
@@ -68606,7 +68606,7 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E738" s="5" t="n">
@@ -84326,7 +84326,7 @@
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E929" s="5" t="n">

--- a/output/pdf_financials_xlsx/CIGI.xlsx
+++ b/output/pdf_financials_xlsx/CIGI.xlsx
@@ -1161,10 +1161,8 @@
       <c r="J16" s="3" t="n">
         <v>139.4</v>
       </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K16" s="3" t="n">
+        <v>-152.047</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>289.554</v>
@@ -1389,10 +1387,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>26.027</v>
+        <v>74.867</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-7.279</v>
+        <v>-7.855</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>47.9</v>
@@ -1415,10 +1413,8 @@
       <c r="J20" s="3" t="n">
         <v>91.571</v>
       </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K20" s="3" t="n">
+        <v>-237.557</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>194.544</v>
@@ -1538,10 +1534,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>26.027</v>
+        <v>74.867</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-7.279</v>
+        <v>-7.855</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>47.9</v>
@@ -1564,10 +1560,8 @@
       <c r="J23" s="3" t="n">
         <v>91.571</v>
       </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K23" s="3" t="n">
+        <v>-237.557</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>194.544</v>
@@ -1846,10 +1840,8 @@
       <c r="J27" s="3" t="n">
         <v>139.4</v>
       </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K27" s="3" t="n">
+        <v>-152.047</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>289.554</v>
@@ -1946,10 +1938,8 @@
       <c r="J29" s="3" t="n">
         <v>160.693</v>
       </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K29" s="3" t="n">
+        <v>-52.826</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>418.295</v>
@@ -1997,10 +1987,8 @@
       <c r="J30" s="3" t="n">
         <v>8.472134058513522</v>
       </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K30" s="3" t="n">
+        <v>-1.29186435546543</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>9.379890556918319</v>
@@ -2048,10 +2036,8 @@
       <c r="J31" s="3" t="n">
         <v>34.3106169296987</v>
       </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K31" s="3" t="n">
+        <v>-56.23918919807691</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>32.81253237738039</v>
@@ -2073,10 +2059,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>1.967747300934466</v>
+        <v>5.660250400701606</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-0.4273664854023727</v>
+        <v>-0.4611847427992358</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>2.411554113210131</v>
@@ -2099,10 +2085,8 @@
       <c r="J32" s="3" t="n">
         <v>4.827850546521265</v>
       </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K32" s="3" t="n">
+        <v>-5.809476785887655</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>4.36247487659455</v>
@@ -5460,10 +5444,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>26.027</v>
+        <v>74.867</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-7.279</v>
+        <v>-7.855</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>47.9</v>
@@ -5486,10 +5470,8 @@
       <c r="J99" s="3" t="n">
         <v>91.571</v>
       </c>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K99" s="3" t="n">
+        <v>-237.557</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>194.544</v>
@@ -5658,31 +5640,31 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>1.397</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-2.614</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>1.348</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-1.796</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-3.897</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>2.261</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-1.377</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-5.88</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="K103" s="3" t="n">
         <v>0</v>
@@ -5805,31 +5787,31 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-25.601</v>
+        <v>-24.204</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>15.259</v>
+        <v>12.645</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>32.008</v>
+        <v>33.356</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-21.18</v>
+        <v>-22.976</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>5.081</v>
+        <v>1.184</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>12.895</v>
+        <v>15.156</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>39.351</v>
+        <v>37.974</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>27.934</v>
+        <v>22.054</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>5.999</v>
+        <v>9.009</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0</v>
@@ -5854,46 +5836,46 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>2.649</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>2.761</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>2.335</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>3.169</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>2.307</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>2.358</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>35.4</v>
+        <v>39.653</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>3.279</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>14.349</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>21.853</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>27.087</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>46.041</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>55.621</v>
       </c>
     </row>
     <row r="108">
@@ -6638,46 +6620,46 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>89.238</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>110.162</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>207.816</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>395.584</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>551.932</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>307.715</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>644.963</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>218.056</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>597.328</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>1629.242</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>0</v>
+        <v>924.98</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>0</v>
+        <v>1938.806</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>0</v>
+        <v>1317.696</v>
       </c>
     </row>
     <row r="124">
@@ -6736,46 +6718,46 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-180.033</v>
+        <v>-90.795</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-143.965</v>
+        <v>-33.803</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-84.79300000000001</v>
+        <v>1.747</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-133.854</v>
+        <v>73.962</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-376.349</v>
+        <v>19.235</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-516.479</v>
+        <v>35.453</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-193.033</v>
+        <v>114.682</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-707.284</v>
+        <v>-62.321</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-201.103</v>
+        <v>16.953</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-819.914</v>
+        <v>-222.586</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-700.201</v>
+        <v>929.0410000000001</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-832.934</v>
+        <v>92.04600000000001</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-1717.233</v>
+        <v>221.573</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-1132.077</v>
+        <v>185.619</v>
       </c>
     </row>
     <row r="126">
@@ -6914,25 +6896,25 @@
         <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0</v>
+        <v>-3.801</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>0</v>
+        <v>-1.808</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0</v>
+        <v>-0.546</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>-0.358</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0</v>
+        <v>-3.029</v>
       </c>
       <c r="J128" s="3" t="n">
         <v>0</v>
@@ -52922,7 +52904,11 @@
           <t>Stock option expense (note 20)</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E545" t="inlineStr">
         <is>
           <t>-</t>
@@ -54656,7 +54642,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E567" s="5" t="n">
         <v>89.238</v>
       </c>
@@ -55890,7 +55880,11 @@
           <t>Stock option expense (note 19)</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr">
         <is>
           <t>-</t>
@@ -57274,7 +57268,11 @@
           <t>Stock option expense (note 21)</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -59170,7 +59168,11 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E623" s="5" t="n">
         <v>1.62</v>
       </c>
@@ -59552,7 +59554,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E628" t="inlineStr">
         <is>
           <t>-</t>
@@ -60842,7 +60848,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
           <t>-</t>
@@ -61390,7 +61400,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E651" s="5" t="n">
         <v>1.397</v>
       </c>
@@ -64652,7 +64666,11 @@
           <t>Stock option expense 2,649</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr"/>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E691" s="5" t="n">
         <v>7.446</v>
       </c>
@@ -66614,7 +66632,11 @@
           <t>Increase in long-term debt 110,162</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr"/>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E714" s="5" t="n">
         <v>206.924</v>
       </c>
@@ -72532,7 +72554,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D786" t="inlineStr"/>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E786" t="inlineStr">
         <is>
           <t>-</t>
@@ -72862,7 +72888,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D790" t="inlineStr"/>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E790" t="inlineStr">
         <is>
           <t>-</t>
@@ -83484,7 +83514,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D919" t="inlineStr"/>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E919" s="5" t="n">
         <v>74.867</v>
       </c>
